--- a/PL2627.xlsx
+++ b/PL2627.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf7844e8cf3277c/Documents/Matt's Stuff/Footy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf7844e8cf3277c/Documents/LMS_2627_1_repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68010DEC-8158-4E01-AB72-369A3BA3C3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{68010DEC-8158-4E01-AB72-369A3BA3C3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE2538F-6084-4796-B45D-94F5BB874201}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="1990" windowWidth="19420" windowHeight="11500" xr2:uid="{36BCC181-D9F5-4121-8B79-8FE9A95C768C}"/>
+    <workbookView xWindow="1335" yWindow="-16860" windowWidth="21600" windowHeight="12525" xr2:uid="{36BCC181-D9F5-4121-8B79-8FE9A95C768C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$381</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -490,13 +490,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4EEE65-7860-43B6-A275-4EB8A0B58B8B}">
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,11 +509,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -526,11 +526,17 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -543,11 +549,17 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -560,11 +572,17 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -577,11 +595,17 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -594,11 +618,17 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -611,11 +641,17 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -628,11 +664,17 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -645,11 +687,17 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1</v>
       </c>
@@ -662,11 +710,17 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -679,11 +733,17 @@
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -696,11 +756,11 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2</v>
       </c>
@@ -713,11 +773,11 @@
       <c r="D13" t="s">
         <v>7</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2</v>
       </c>
@@ -730,11 +790,11 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2</v>
       </c>
@@ -747,11 +807,11 @@
       <c r="D15" t="s">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2</v>
       </c>
@@ -764,11 +824,11 @@
       <c r="D16" t="s">
         <v>23</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2</v>
       </c>
@@ -781,11 +841,11 @@
       <c r="D17" t="s">
         <v>9</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2</v>
       </c>
@@ -798,11 +858,11 @@
       <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2</v>
       </c>
@@ -815,11 +875,11 @@
       <c r="D19" t="s">
         <v>19</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2</v>
       </c>
@@ -832,11 +892,11 @@
       <c r="D20" t="s">
         <v>22</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2</v>
       </c>
@@ -849,11 +909,11 @@
       <c r="D21" t="s">
         <v>6</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>3</v>
       </c>
@@ -866,11 +926,11 @@
       <c r="D22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>3</v>
       </c>
@@ -883,11 +943,11 @@
       <c r="D23" t="s">
         <v>24</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>3</v>
       </c>
@@ -900,11 +960,11 @@
       <c r="D24" t="s">
         <v>8</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>3</v>
       </c>
@@ -917,11 +977,11 @@
       <c r="D25" t="s">
         <v>13</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>3</v>
       </c>
@@ -934,11 +994,11 @@
       <c r="D26" t="s">
         <v>14</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>3</v>
       </c>
@@ -951,11 +1011,11 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>3</v>
       </c>
@@ -968,11 +1028,11 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>3</v>
       </c>
@@ -985,11 +1045,11 @@
       <c r="D29" t="s">
         <v>21</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1002,11 +1062,11 @@
       <c r="D30" t="s">
         <v>5</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1019,11 +1079,11 @@
       <c r="D31" t="s">
         <v>12</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>4</v>
       </c>
@@ -1036,11 +1096,11 @@
       <c r="D32" t="s">
         <v>6</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1053,11 +1113,11 @@
       <c r="D33" t="s">
         <v>7</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>4</v>
       </c>
@@ -1070,11 +1130,11 @@
       <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>4</v>
       </c>
@@ -1087,11 +1147,11 @@
       <c r="D35" t="s">
         <v>11</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4</v>
       </c>
@@ -1104,11 +1164,11 @@
       <c r="D36" t="s">
         <v>17</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>4</v>
       </c>
@@ -1121,11 +1181,11 @@
       <c r="D37" t="s">
         <v>22</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>4</v>
       </c>
@@ -1138,11 +1198,11 @@
       <c r="D38" t="s">
         <v>23</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>4</v>
       </c>
@@ -1155,11 +1215,11 @@
       <c r="D39" t="s">
         <v>10</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>4</v>
       </c>
@@ -1172,11 +1232,11 @@
       <c r="D40" t="s">
         <v>19</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>4</v>
       </c>
@@ -1189,11 +1249,11 @@
       <c r="D41" t="s">
         <v>16</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>5</v>
       </c>
@@ -1206,11 +1266,11 @@
       <c r="D42" t="s">
         <v>24</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>5</v>
       </c>
@@ -1223,11 +1283,11 @@
       <c r="D43" t="s">
         <v>8</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>5</v>
       </c>
@@ -1240,11 +1300,11 @@
       <c r="D44" t="s">
         <v>12</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>5</v>
       </c>
@@ -1257,11 +1317,11 @@
       <c r="D45" t="s">
         <v>16</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>5</v>
       </c>
@@ -1274,11 +1334,11 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>5</v>
       </c>
@@ -1291,11 +1351,11 @@
       <c r="D47" t="s">
         <v>20</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>5</v>
       </c>
@@ -1308,11 +1368,11 @@
       <c r="D48" t="s">
         <v>21</v>
       </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>5</v>
       </c>
@@ -1325,11 +1385,11 @@
       <c r="D49" t="s">
         <v>23</v>
       </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>5</v>
       </c>
@@ -1342,11 +1402,11 @@
       <c r="D50" t="s">
         <v>7</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1359,11 +1419,11 @@
       <c r="D51" t="s">
         <v>13</v>
       </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>6</v>
       </c>
@@ -1376,11 +1436,11 @@
       <c r="D52" t="s">
         <v>5</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>6</v>
       </c>
@@ -1393,11 +1453,11 @@
       <c r="D53" t="s">
         <v>6</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>6</v>
       </c>
@@ -1410,11 +1470,11 @@
       <c r="D54" t="s">
         <v>9</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>6</v>
       </c>
@@ -1427,11 +1487,11 @@
       <c r="D55" t="s">
         <v>10</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>6</v>
       </c>
@@ -1444,11 +1504,11 @@
       <c r="D56" t="s">
         <v>11</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>6</v>
       </c>
@@ -1461,11 +1521,11 @@
       <c r="D57" t="s">
         <v>14</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>6</v>
       </c>
@@ -1478,11 +1538,11 @@
       <c r="D58" t="s">
         <v>15</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>6</v>
       </c>
@@ -1495,11 +1555,11 @@
       <c r="D59" t="s">
         <v>17</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>6</v>
       </c>
@@ -1512,11 +1572,11 @@
       <c r="D60" t="s">
         <v>19</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>6</v>
       </c>
@@ -1529,11 +1589,11 @@
       <c r="D61" t="s">
         <v>22</v>
       </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>7</v>
       </c>
@@ -1546,11 +1606,11 @@
       <c r="D62" t="s">
         <v>7</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>7</v>
       </c>
@@ -1563,11 +1623,11 @@
       <c r="D63" t="s">
         <v>24</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>7</v>
       </c>
@@ -1580,11 +1640,11 @@
       <c r="D64" t="s">
         <v>8</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>7</v>
       </c>
@@ -1597,11 +1657,11 @@
       <c r="D65" t="s">
         <v>12</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>7</v>
       </c>
@@ -1614,11 +1674,11 @@
       <c r="D66" t="s">
         <v>13</v>
       </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>7</v>
       </c>
@@ -1631,11 +1691,11 @@
       <c r="D67" t="s">
         <v>16</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>7</v>
       </c>
@@ -1648,11 +1708,11 @@
       <c r="D68" t="s">
         <v>18</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>7</v>
       </c>
@@ -1665,11 +1725,11 @@
       <c r="D69" t="s">
         <v>20</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>7</v>
       </c>
@@ -1682,11 +1742,11 @@
       <c r="D70" t="s">
         <v>21</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>7</v>
       </c>
@@ -1699,11 +1759,11 @@
       <c r="D71" t="s">
         <v>23</v>
       </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>8</v>
       </c>
@@ -1716,11 +1776,11 @@
       <c r="D72" t="s">
         <v>5</v>
       </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>8</v>
       </c>
@@ -1733,11 +1793,11 @@
       <c r="D73" t="s">
         <v>6</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>8</v>
       </c>
@@ -1750,11 +1810,11 @@
       <c r="D74" t="s">
         <v>9</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>8</v>
       </c>
@@ -1767,11 +1827,11 @@
       <c r="D75" t="s">
         <v>10</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>8</v>
       </c>
@@ -1784,11 +1844,11 @@
       <c r="D76" t="s">
         <v>11</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>8</v>
       </c>
@@ -1801,11 +1861,11 @@
       <c r="D77" t="s">
         <v>14</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>8</v>
       </c>
@@ -1818,11 +1878,11 @@
       <c r="D78" t="s">
         <v>15</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>8</v>
       </c>
@@ -1835,11 +1895,11 @@
       <c r="D79" t="s">
         <v>17</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>8</v>
       </c>
@@ -1852,11 +1912,11 @@
       <c r="D80" t="s">
         <v>19</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>8</v>
       </c>
@@ -1869,11 +1929,11 @@
       <c r="D81" t="s">
         <v>22</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>9</v>
       </c>
@@ -1886,11 +1946,11 @@
       <c r="D82" t="s">
         <v>6</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>9</v>
       </c>
@@ -1903,11 +1963,11 @@
       <c r="D83" t="s">
         <v>7</v>
       </c>
-      <c r="E83" t="s">
+      <c r="G83" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>9</v>
       </c>
@@ -1920,11 +1980,11 @@
       <c r="D84" t="s">
         <v>24</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>9</v>
       </c>
@@ -1937,11 +1997,11 @@
       <c r="D85" t="s">
         <v>9</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>9</v>
       </c>
@@ -1954,11 +2014,11 @@
       <c r="D86" t="s">
         <v>10</v>
       </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>9</v>
       </c>
@@ -1971,11 +2031,11 @@
       <c r="D87" t="s">
         <v>14</v>
       </c>
-      <c r="E87" t="s">
+      <c r="G87" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>9</v>
       </c>
@@ -1988,11 +2048,11 @@
       <c r="D88" t="s">
         <v>17</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>9</v>
       </c>
@@ -2005,11 +2065,11 @@
       <c r="D89" t="s">
         <v>18</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>9</v>
       </c>
@@ -2022,11 +2082,11 @@
       <c r="D90" t="s">
         <v>20</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>9</v>
       </c>
@@ -2039,11 +2099,11 @@
       <c r="D91" t="s">
         <v>23</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>10</v>
       </c>
@@ -2056,11 +2116,11 @@
       <c r="D92" t="s">
         <v>5</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>10</v>
       </c>
@@ -2073,11 +2133,11 @@
       <c r="D93" t="s">
         <v>8</v>
       </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>10</v>
       </c>
@@ -2090,11 +2150,11 @@
       <c r="D94" t="s">
         <v>11</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>10</v>
       </c>
@@ -2107,11 +2167,11 @@
       <c r="D95" t="s">
         <v>12</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>10</v>
       </c>
@@ -2124,11 +2184,11 @@
       <c r="D96" t="s">
         <v>13</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>10</v>
       </c>
@@ -2141,11 +2201,11 @@
       <c r="D97" t="s">
         <v>15</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>10</v>
       </c>
@@ -2158,11 +2218,11 @@
       <c r="D98" t="s">
         <v>16</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>10</v>
       </c>
@@ -2175,11 +2235,11 @@
       <c r="D99" t="s">
         <v>19</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>10</v>
       </c>
@@ -2192,11 +2252,11 @@
       <c r="D100" t="s">
         <v>21</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>10</v>
       </c>
@@ -2209,11 +2269,11 @@
       <c r="D101" t="s">
         <v>22</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>11</v>
       </c>
@@ -2226,11 +2286,11 @@
       <c r="D102" t="s">
         <v>6</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>11</v>
       </c>
@@ -2243,11 +2303,11 @@
       <c r="D103" t="s">
         <v>7</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>11</v>
       </c>
@@ -2260,11 +2320,11 @@
       <c r="D104" t="s">
         <v>24</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>11</v>
       </c>
@@ -2277,11 +2337,11 @@
       <c r="D105" t="s">
         <v>9</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>11</v>
       </c>
@@ -2294,11 +2354,11 @@
       <c r="D106" t="s">
         <v>10</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>11</v>
       </c>
@@ -2311,11 +2371,11 @@
       <c r="D107" t="s">
         <v>14</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>11</v>
       </c>
@@ -2328,11 +2388,11 @@
       <c r="D108" t="s">
         <v>17</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>11</v>
       </c>
@@ -2345,11 +2405,11 @@
       <c r="D109" t="s">
         <v>18</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>11</v>
       </c>
@@ -2362,11 +2422,11 @@
       <c r="D110" t="s">
         <v>20</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>11</v>
       </c>
@@ -2379,11 +2439,11 @@
       <c r="D111" t="s">
         <v>23</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>12</v>
       </c>
@@ -2396,11 +2456,11 @@
       <c r="D112" t="s">
         <v>5</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>12</v>
       </c>
@@ -2413,11 +2473,11 @@
       <c r="D113" t="s">
         <v>8</v>
       </c>
-      <c r="E113" t="s">
+      <c r="G113" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>12</v>
       </c>
@@ -2430,11 +2490,11 @@
       <c r="D114" t="s">
         <v>11</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>12</v>
       </c>
@@ -2447,11 +2507,11 @@
       <c r="D115" t="s">
         <v>12</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>12</v>
       </c>
@@ -2464,11 +2524,11 @@
       <c r="D116" t="s">
         <v>13</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>12</v>
       </c>
@@ -2481,11 +2541,11 @@
       <c r="D117" t="s">
         <v>15</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>12</v>
       </c>
@@ -2498,11 +2558,11 @@
       <c r="D118" t="s">
         <v>16</v>
       </c>
-      <c r="E118" t="s">
+      <c r="G118" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>12</v>
       </c>
@@ -2515,11 +2575,11 @@
       <c r="D119" t="s">
         <v>19</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>12</v>
       </c>
@@ -2532,11 +2592,11 @@
       <c r="D120" t="s">
         <v>21</v>
       </c>
-      <c r="E120" t="s">
+      <c r="G120" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>12</v>
       </c>
@@ -2549,11 +2609,11 @@
       <c r="D121" t="s">
         <v>22</v>
       </c>
-      <c r="E121" t="s">
+      <c r="G121" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>13</v>
       </c>
@@ -2566,11 +2626,11 @@
       <c r="D122" t="s">
         <v>6</v>
       </c>
-      <c r="E122" t="s">
+      <c r="G122" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>13</v>
       </c>
@@ -2583,11 +2643,11 @@
       <c r="D123" t="s">
         <v>7</v>
       </c>
-      <c r="E123" t="s">
+      <c r="G123" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>13</v>
       </c>
@@ -2600,11 +2660,11 @@
       <c r="D124" t="s">
         <v>24</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>13</v>
       </c>
@@ -2617,11 +2677,11 @@
       <c r="D125" t="s">
         <v>9</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>13</v>
       </c>
@@ -2634,11 +2694,11 @@
       <c r="D126" t="s">
         <v>10</v>
       </c>
-      <c r="E126" t="s">
+      <c r="G126" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>13</v>
       </c>
@@ -2651,11 +2711,11 @@
       <c r="D127" t="s">
         <v>14</v>
       </c>
-      <c r="E127" t="s">
+      <c r="G127" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>13</v>
       </c>
@@ -2668,11 +2728,11 @@
       <c r="D128" t="s">
         <v>17</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>13</v>
       </c>
@@ -2685,11 +2745,11 @@
       <c r="D129" t="s">
         <v>18</v>
       </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>13</v>
       </c>
@@ -2702,11 +2762,11 @@
       <c r="D130" t="s">
         <v>20</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>13</v>
       </c>
@@ -2719,11 +2779,11 @@
       <c r="D131" t="s">
         <v>23</v>
       </c>
-      <c r="E131" t="s">
+      <c r="G131" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>14</v>
       </c>
@@ -2736,11 +2796,11 @@
       <c r="D132" t="s">
         <v>6</v>
       </c>
-      <c r="E132" t="s">
+      <c r="G132" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>14</v>
       </c>
@@ -2753,11 +2813,11 @@
       <c r="D133" t="s">
         <v>7</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>14</v>
       </c>
@@ -2770,11 +2830,11 @@
       <c r="D134" t="s">
         <v>24</v>
       </c>
-      <c r="E134" t="s">
+      <c r="G134" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>14</v>
       </c>
@@ -2787,11 +2847,11 @@
       <c r="D135" t="s">
         <v>9</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>14</v>
       </c>
@@ -2804,11 +2864,11 @@
       <c r="D136" t="s">
         <v>12</v>
       </c>
-      <c r="E136" t="s">
+      <c r="G136" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>14</v>
       </c>
@@ -2821,11 +2881,11 @@
       <c r="D137" t="s">
         <v>16</v>
       </c>
-      <c r="E137" t="s">
+      <c r="G137" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>14</v>
       </c>
@@ -2838,11 +2898,11 @@
       <c r="D138" t="s">
         <v>19</v>
       </c>
-      <c r="E138" t="s">
+      <c r="G138" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>14</v>
       </c>
@@ -2855,11 +2915,11 @@
       <c r="D139" t="s">
         <v>20</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>14</v>
       </c>
@@ -2872,11 +2932,11 @@
       <c r="D140" t="s">
         <v>21</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>14</v>
       </c>
@@ -2889,11 +2949,11 @@
       <c r="D141" t="s">
         <v>23</v>
       </c>
-      <c r="E141" t="s">
+      <c r="G141" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>15</v>
       </c>
@@ -2906,11 +2966,11 @@
       <c r="D142" t="s">
         <v>5</v>
       </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>15</v>
       </c>
@@ -2923,11 +2983,11 @@
       <c r="D143" t="s">
         <v>8</v>
       </c>
-      <c r="E143" t="s">
+      <c r="G143" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>15</v>
       </c>
@@ -2940,11 +3000,11 @@
       <c r="D144" t="s">
         <v>10</v>
       </c>
-      <c r="E144" t="s">
+      <c r="G144" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>15</v>
       </c>
@@ -2957,11 +3017,11 @@
       <c r="D145" t="s">
         <v>11</v>
       </c>
-      <c r="E145" t="s">
+      <c r="G145" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>15</v>
       </c>
@@ -2974,11 +3034,11 @@
       <c r="D146" t="s">
         <v>13</v>
       </c>
-      <c r="E146" t="s">
+      <c r="G146" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>15</v>
       </c>
@@ -2991,11 +3051,11 @@
       <c r="D147" t="s">
         <v>14</v>
       </c>
-      <c r="E147" t="s">
+      <c r="G147" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>15</v>
       </c>
@@ -3008,11 +3068,11 @@
       <c r="D148" t="s">
         <v>15</v>
       </c>
-      <c r="E148" t="s">
+      <c r="G148" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>15</v>
       </c>
@@ -3025,11 +3085,11 @@
       <c r="D149" t="s">
         <v>17</v>
       </c>
-      <c r="E149" t="s">
+      <c r="G149" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>15</v>
       </c>
@@ -3042,11 +3102,11 @@
       <c r="D150" t="s">
         <v>18</v>
       </c>
-      <c r="E150" t="s">
+      <c r="G150" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>15</v>
       </c>
@@ -3059,11 +3119,11 @@
       <c r="D151" t="s">
         <v>22</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>16</v>
       </c>
@@ -3076,11 +3136,11 @@
       <c r="D152" t="s">
         <v>5</v>
       </c>
-      <c r="E152" t="s">
+      <c r="G152" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>16</v>
       </c>
@@ -3093,11 +3153,11 @@
       <c r="D153" t="s">
         <v>7</v>
       </c>
-      <c r="E153" t="s">
+      <c r="G153" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>16</v>
       </c>
@@ -3110,11 +3170,11 @@
       <c r="D154" t="s">
         <v>24</v>
       </c>
-      <c r="E154" t="s">
+      <c r="G154" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>16</v>
       </c>
@@ -3127,11 +3187,11 @@
       <c r="D155" t="s">
         <v>8</v>
       </c>
-      <c r="E155" t="s">
+      <c r="G155" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>16</v>
       </c>
@@ -3144,11 +3204,11 @@
       <c r="D156" t="s">
         <v>9</v>
       </c>
-      <c r="E156" t="s">
+      <c r="G156" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>16</v>
       </c>
@@ -3161,11 +3221,11 @@
       <c r="D157" t="s">
         <v>16</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>16</v>
       </c>
@@ -3178,11 +3238,11 @@
       <c r="D158" t="s">
         <v>17</v>
       </c>
-      <c r="E158" t="s">
+      <c r="G158" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>16</v>
       </c>
@@ -3195,11 +3255,11 @@
       <c r="D159" t="s">
         <v>18</v>
       </c>
-      <c r="E159" t="s">
+      <c r="G159" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>16</v>
       </c>
@@ -3212,11 +3272,11 @@
       <c r="D160" t="s">
         <v>21</v>
       </c>
-      <c r="E160" t="s">
+      <c r="G160" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>16</v>
       </c>
@@ -3229,11 +3289,11 @@
       <c r="D161" t="s">
         <v>22</v>
       </c>
-      <c r="E161" t="s">
+      <c r="G161" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>17</v>
       </c>
@@ -3246,11 +3306,11 @@
       <c r="D162" t="s">
         <v>6</v>
       </c>
-      <c r="E162" t="s">
+      <c r="G162" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>17</v>
       </c>
@@ -3263,11 +3323,11 @@
       <c r="D163" t="s">
         <v>10</v>
       </c>
-      <c r="E163" t="s">
+      <c r="G163" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>17</v>
       </c>
@@ -3280,11 +3340,11 @@
       <c r="D164" t="s">
         <v>11</v>
       </c>
-      <c r="E164" t="s">
+      <c r="G164" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>17</v>
       </c>
@@ -3297,11 +3357,11 @@
       <c r="D165" t="s">
         <v>12</v>
       </c>
-      <c r="E165" t="s">
+      <c r="G165" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>17</v>
       </c>
@@ -3314,11 +3374,11 @@
       <c r="D166" t="s">
         <v>13</v>
       </c>
-      <c r="E166" t="s">
+      <c r="G166" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>17</v>
       </c>
@@ -3331,11 +3391,11 @@
       <c r="D167" t="s">
         <v>14</v>
       </c>
-      <c r="E167" t="s">
+      <c r="G167" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>17</v>
       </c>
@@ -3348,11 +3408,11 @@
       <c r="D168" t="s">
         <v>15</v>
       </c>
-      <c r="E168" t="s">
+      <c r="G168" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>17</v>
       </c>
@@ -3365,11 +3425,11 @@
       <c r="D169" t="s">
         <v>19</v>
       </c>
-      <c r="E169" t="s">
+      <c r="G169" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>17</v>
       </c>
@@ -3382,11 +3442,11 @@
       <c r="D170" t="s">
         <v>20</v>
       </c>
-      <c r="E170" t="s">
+      <c r="G170" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>17</v>
       </c>
@@ -3399,11 +3459,11 @@
       <c r="D171" t="s">
         <v>23</v>
       </c>
-      <c r="E171" t="s">
+      <c r="G171" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>18</v>
       </c>
@@ -3416,11 +3476,11 @@
       <c r="D172" t="s">
         <v>6</v>
       </c>
-      <c r="E172" t="s">
+      <c r="G172" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>18</v>
       </c>
@@ -3433,11 +3493,11 @@
       <c r="D173" t="s">
         <v>10</v>
       </c>
-      <c r="E173" t="s">
+      <c r="G173" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>18</v>
       </c>
@@ -3450,11 +3510,11 @@
       <c r="D174" t="s">
         <v>11</v>
       </c>
-      <c r="E174" t="s">
+      <c r="G174" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>18</v>
       </c>
@@ -3467,11 +3527,11 @@
       <c r="D175" t="s">
         <v>12</v>
       </c>
-      <c r="E175" t="s">
+      <c r="G175" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>18</v>
       </c>
@@ -3484,11 +3544,11 @@
       <c r="D176" t="s">
         <v>13</v>
       </c>
-      <c r="E176" t="s">
+      <c r="G176" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>18</v>
       </c>
@@ -3501,11 +3561,11 @@
       <c r="D177" t="s">
         <v>14</v>
       </c>
-      <c r="E177" t="s">
+      <c r="G177" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>18</v>
       </c>
@@ -3518,11 +3578,11 @@
       <c r="D178" t="s">
         <v>15</v>
       </c>
-      <c r="E178" t="s">
+      <c r="G178" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>18</v>
       </c>
@@ -3535,11 +3595,11 @@
       <c r="D179" t="s">
         <v>19</v>
       </c>
-      <c r="E179" t="s">
+      <c r="G179" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>18</v>
       </c>
@@ -3552,11 +3612,11 @@
       <c r="D180" t="s">
         <v>20</v>
       </c>
-      <c r="E180" t="s">
+      <c r="G180" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>18</v>
       </c>
@@ -3569,11 +3629,11 @@
       <c r="D181" t="s">
         <v>23</v>
       </c>
-      <c r="E181" t="s">
+      <c r="G181" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>19</v>
       </c>
@@ -3586,11 +3646,11 @@
       <c r="D182" t="s">
         <v>5</v>
       </c>
-      <c r="E182" t="s">
+      <c r="G182" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>19</v>
       </c>
@@ -3603,11 +3663,11 @@
       <c r="D183" t="s">
         <v>7</v>
       </c>
-      <c r="E183" t="s">
+      <c r="G183" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>19</v>
       </c>
@@ -3620,11 +3680,11 @@
       <c r="D184" t="s">
         <v>24</v>
       </c>
-      <c r="E184" t="s">
+      <c r="G184" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>19</v>
       </c>
@@ -3637,11 +3697,11 @@
       <c r="D185" t="s">
         <v>8</v>
       </c>
-      <c r="E185" t="s">
+      <c r="G185" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>19</v>
       </c>
@@ -3654,11 +3714,11 @@
       <c r="D186" t="s">
         <v>9</v>
       </c>
-      <c r="E186" t="s">
+      <c r="G186" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>19</v>
       </c>
@@ -3671,11 +3731,11 @@
       <c r="D187" t="s">
         <v>16</v>
       </c>
-      <c r="E187" t="s">
+      <c r="G187" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>19</v>
       </c>
@@ -3688,11 +3748,11 @@
       <c r="D188" t="s">
         <v>17</v>
       </c>
-      <c r="E188" t="s">
+      <c r="G188" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>19</v>
       </c>
@@ -3705,11 +3765,11 @@
       <c r="D189" t="s">
         <v>18</v>
       </c>
-      <c r="E189" t="s">
+      <c r="G189" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>19</v>
       </c>
@@ -3722,11 +3782,11 @@
       <c r="D190" t="s">
         <v>21</v>
       </c>
-      <c r="E190" t="s">
+      <c r="G190" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>19</v>
       </c>
@@ -3739,11 +3799,11 @@
       <c r="D191" t="s">
         <v>22</v>
       </c>
-      <c r="E191" t="s">
+      <c r="G191" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>20</v>
       </c>
@@ -3756,11 +3816,11 @@
       <c r="D192" t="s">
         <v>5</v>
       </c>
-      <c r="E192" t="s">
+      <c r="G192" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>20</v>
       </c>
@@ -3773,11 +3833,11 @@
       <c r="D193" t="s">
         <v>8</v>
       </c>
-      <c r="E193" t="s">
+      <c r="G193" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>20</v>
       </c>
@@ -3790,11 +3850,11 @@
       <c r="D194" t="s">
         <v>11</v>
       </c>
-      <c r="E194" t="s">
+      <c r="G194" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>20</v>
       </c>
@@ -3807,11 +3867,11 @@
       <c r="D195" t="s">
         <v>12</v>
       </c>
-      <c r="E195" t="s">
+      <c r="G195" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>20</v>
       </c>
@@ -3824,11 +3884,11 @@
       <c r="D196" t="s">
         <v>13</v>
       </c>
-      <c r="E196" t="s">
+      <c r="G196" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>20</v>
       </c>
@@ -3841,11 +3901,11 @@
       <c r="D197" t="s">
         <v>15</v>
       </c>
-      <c r="E197" t="s">
+      <c r="G197" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>20</v>
       </c>
@@ -3858,11 +3918,11 @@
       <c r="D198" t="s">
         <v>16</v>
       </c>
-      <c r="E198" t="s">
+      <c r="G198" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>20</v>
       </c>
@@ -3875,11 +3935,11 @@
       <c r="D199" t="s">
         <v>19</v>
       </c>
-      <c r="E199" t="s">
+      <c r="G199" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>20</v>
       </c>
@@ -3892,11 +3952,11 @@
       <c r="D200" t="s">
         <v>21</v>
       </c>
-      <c r="E200" t="s">
+      <c r="G200" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>20</v>
       </c>
@@ -3909,11 +3969,11 @@
       <c r="D201" t="s">
         <v>22</v>
       </c>
-      <c r="E201" t="s">
+      <c r="G201" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>21</v>
       </c>
@@ -3926,11 +3986,11 @@
       <c r="D202" t="s">
         <v>6</v>
       </c>
-      <c r="E202" t="s">
+      <c r="G202" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>21</v>
       </c>
@@ -3943,11 +4003,11 @@
       <c r="D203" t="s">
         <v>7</v>
       </c>
-      <c r="E203" t="s">
+      <c r="G203" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>21</v>
       </c>
@@ -3960,11 +4020,11 @@
       <c r="D204" t="s">
         <v>24</v>
       </c>
-      <c r="E204" t="s">
+      <c r="G204" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>21</v>
       </c>
@@ -3977,11 +4037,11 @@
       <c r="D205" t="s">
         <v>9</v>
       </c>
-      <c r="E205" t="s">
+      <c r="G205" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>21</v>
       </c>
@@ -3994,11 +4054,11 @@
       <c r="D206" t="s">
         <v>10</v>
       </c>
-      <c r="E206" t="s">
+      <c r="G206" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>21</v>
       </c>
@@ -4011,11 +4071,11 @@
       <c r="D207" t="s">
         <v>14</v>
       </c>
-      <c r="E207" t="s">
+      <c r="G207" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>21</v>
       </c>
@@ -4028,11 +4088,11 @@
       <c r="D208" t="s">
         <v>17</v>
       </c>
-      <c r="E208" t="s">
+      <c r="G208" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>21</v>
       </c>
@@ -4045,11 +4105,11 @@
       <c r="D209" t="s">
         <v>18</v>
       </c>
-      <c r="E209" t="s">
+      <c r="G209" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>21</v>
       </c>
@@ -4062,11 +4122,11 @@
       <c r="D210" t="s">
         <v>20</v>
       </c>
-      <c r="E210" t="s">
+      <c r="G210" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>21</v>
       </c>
@@ -4079,11 +4139,11 @@
       <c r="D211" t="s">
         <v>23</v>
       </c>
-      <c r="E211" t="s">
+      <c r="G211" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>22</v>
       </c>
@@ -4096,11 +4156,11 @@
       <c r="D212" t="s">
         <v>5</v>
       </c>
-      <c r="E212" t="s">
+      <c r="G212" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>22</v>
       </c>
@@ -4113,11 +4173,11 @@
       <c r="D213" t="s">
         <v>8</v>
       </c>
-      <c r="E213" t="s">
+      <c r="G213" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>22</v>
       </c>
@@ -4130,11 +4190,11 @@
       <c r="D214" t="s">
         <v>11</v>
       </c>
-      <c r="E214" t="s">
+      <c r="G214" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>22</v>
       </c>
@@ -4147,11 +4207,11 @@
       <c r="D215" t="s">
         <v>12</v>
       </c>
-      <c r="E215" t="s">
+      <c r="G215" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>22</v>
       </c>
@@ -4164,11 +4224,11 @@
       <c r="D216" t="s">
         <v>13</v>
       </c>
-      <c r="E216" t="s">
+      <c r="G216" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>22</v>
       </c>
@@ -4181,11 +4241,11 @@
       <c r="D217" t="s">
         <v>15</v>
       </c>
-      <c r="E217" t="s">
+      <c r="G217" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>22</v>
       </c>
@@ -4198,11 +4258,11 @@
       <c r="D218" t="s">
         <v>16</v>
       </c>
-      <c r="E218" t="s">
+      <c r="G218" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>22</v>
       </c>
@@ -4215,11 +4275,11 @@
       <c r="D219" t="s">
         <v>19</v>
       </c>
-      <c r="E219" t="s">
+      <c r="G219" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>22</v>
       </c>
@@ -4232,11 +4292,11 @@
       <c r="D220" t="s">
         <v>21</v>
       </c>
-      <c r="E220" t="s">
+      <c r="G220" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>22</v>
       </c>
@@ -4249,11 +4309,11 @@
       <c r="D221" t="s">
         <v>22</v>
       </c>
-      <c r="E221" t="s">
+      <c r="G221" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>23</v>
       </c>
@@ -4266,11 +4326,11 @@
       <c r="D222" t="s">
         <v>6</v>
       </c>
-      <c r="E222" t="s">
+      <c r="G222" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>23</v>
       </c>
@@ -4283,11 +4343,11 @@
       <c r="D223" t="s">
         <v>7</v>
       </c>
-      <c r="E223" t="s">
+      <c r="G223" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>23</v>
       </c>
@@ -4300,11 +4360,11 @@
       <c r="D224" t="s">
         <v>24</v>
       </c>
-      <c r="E224" t="s">
+      <c r="G224" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>23</v>
       </c>
@@ -4317,11 +4377,11 @@
       <c r="D225" t="s">
         <v>9</v>
       </c>
-      <c r="E225" t="s">
+      <c r="G225" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>23</v>
       </c>
@@ -4334,11 +4394,11 @@
       <c r="D226" t="s">
         <v>10</v>
       </c>
-      <c r="E226" t="s">
+      <c r="G226" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>23</v>
       </c>
@@ -4351,11 +4411,11 @@
       <c r="D227" t="s">
         <v>14</v>
       </c>
-      <c r="E227" t="s">
+      <c r="G227" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>23</v>
       </c>
@@ -4368,11 +4428,11 @@
       <c r="D228" t="s">
         <v>17</v>
       </c>
-      <c r="E228" t="s">
+      <c r="G228" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>23</v>
       </c>
@@ -4385,11 +4445,11 @@
       <c r="D229" t="s">
         <v>18</v>
       </c>
-      <c r="E229" t="s">
+      <c r="G229" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>23</v>
       </c>
@@ -4402,11 +4462,11 @@
       <c r="D230" t="s">
         <v>20</v>
       </c>
-      <c r="E230" t="s">
+      <c r="G230" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>23</v>
       </c>
@@ -4419,11 +4479,11 @@
       <c r="D231" t="s">
         <v>23</v>
       </c>
-      <c r="E231" t="s">
+      <c r="G231" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>24</v>
       </c>
@@ -4436,11 +4496,11 @@
       <c r="D232" t="s">
         <v>5</v>
       </c>
-      <c r="E232" t="s">
+      <c r="G232" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>24</v>
       </c>
@@ -4453,11 +4513,11 @@
       <c r="D233" t="s">
         <v>8</v>
       </c>
-      <c r="E233" t="s">
+      <c r="G233" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>24</v>
       </c>
@@ -4470,11 +4530,11 @@
       <c r="D234" t="s">
         <v>11</v>
       </c>
-      <c r="E234" t="s">
+      <c r="G234" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>24</v>
       </c>
@@ -4487,11 +4547,11 @@
       <c r="D235" t="s">
         <v>12</v>
       </c>
-      <c r="E235" t="s">
+      <c r="G235" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>24</v>
       </c>
@@ -4504,11 +4564,11 @@
       <c r="D236" t="s">
         <v>13</v>
       </c>
-      <c r="E236" t="s">
+      <c r="G236" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>24</v>
       </c>
@@ -4521,11 +4581,11 @@
       <c r="D237" t="s">
         <v>15</v>
       </c>
-      <c r="E237" t="s">
+      <c r="G237" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>24</v>
       </c>
@@ -4538,11 +4598,11 @@
       <c r="D238" t="s">
         <v>16</v>
       </c>
-      <c r="E238" t="s">
+      <c r="G238" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>24</v>
       </c>
@@ -4555,11 +4615,11 @@
       <c r="D239" t="s">
         <v>19</v>
       </c>
-      <c r="E239" t="s">
+      <c r="G239" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>24</v>
       </c>
@@ -4572,11 +4632,11 @@
       <c r="D240" t="s">
         <v>21</v>
       </c>
-      <c r="E240" t="s">
+      <c r="G240" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>24</v>
       </c>
@@ -4589,11 +4649,11 @@
       <c r="D241" t="s">
         <v>22</v>
       </c>
-      <c r="E241" t="s">
+      <c r="G241" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>25</v>
       </c>
@@ -4606,11 +4666,11 @@
       <c r="D242" t="s">
         <v>6</v>
       </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>25</v>
       </c>
@@ -4623,11 +4683,11 @@
       <c r="D243" t="s">
         <v>10</v>
       </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>25</v>
       </c>
@@ -4640,11 +4700,11 @@
       <c r="D244" t="s">
         <v>11</v>
       </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>25</v>
       </c>
@@ -4657,11 +4717,11 @@
       <c r="D245" t="s">
         <v>12</v>
       </c>
-      <c r="E245" t="s">
+      <c r="G245" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>25</v>
       </c>
@@ -4674,11 +4734,11 @@
       <c r="D246" t="s">
         <v>13</v>
       </c>
-      <c r="E246" t="s">
+      <c r="G246" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>25</v>
       </c>
@@ -4691,11 +4751,11 @@
       <c r="D247" t="s">
         <v>14</v>
       </c>
-      <c r="E247" t="s">
+      <c r="G247" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>25</v>
       </c>
@@ -4708,11 +4768,11 @@
       <c r="D248" t="s">
         <v>15</v>
       </c>
-      <c r="E248" t="s">
+      <c r="G248" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>25</v>
       </c>
@@ -4725,11 +4785,11 @@
       <c r="D249" t="s">
         <v>19</v>
       </c>
-      <c r="E249" t="s">
+      <c r="G249" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>25</v>
       </c>
@@ -4742,11 +4802,11 @@
       <c r="D250" t="s">
         <v>20</v>
       </c>
-      <c r="E250" t="s">
+      <c r="G250" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>25</v>
       </c>
@@ -4759,11 +4819,11 @@
       <c r="D251" t="s">
         <v>23</v>
       </c>
-      <c r="E251" t="s">
+      <c r="G251" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>26</v>
       </c>
@@ -4776,11 +4836,11 @@
       <c r="D252" t="s">
         <v>5</v>
       </c>
-      <c r="E252" t="s">
+      <c r="G252" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>26</v>
       </c>
@@ -4793,11 +4853,11 @@
       <c r="D253" t="s">
         <v>7</v>
       </c>
-      <c r="E253" t="s">
+      <c r="G253" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>26</v>
       </c>
@@ -4810,11 +4870,11 @@
       <c r="D254" t="s">
         <v>24</v>
       </c>
-      <c r="E254" t="s">
+      <c r="G254" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>26</v>
       </c>
@@ -4827,11 +4887,11 @@
       <c r="D255" t="s">
         <v>8</v>
       </c>
-      <c r="E255" t="s">
+      <c r="G255" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>26</v>
       </c>
@@ -4844,11 +4904,11 @@
       <c r="D256" t="s">
         <v>9</v>
       </c>
-      <c r="E256" t="s">
+      <c r="G256" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>26</v>
       </c>
@@ -4861,11 +4921,11 @@
       <c r="D257" t="s">
         <v>16</v>
       </c>
-      <c r="E257" t="s">
+      <c r="G257" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>26</v>
       </c>
@@ -4878,11 +4938,11 @@
       <c r="D258" t="s">
         <v>17</v>
       </c>
-      <c r="E258" t="s">
+      <c r="G258" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>26</v>
       </c>
@@ -4895,11 +4955,11 @@
       <c r="D259" t="s">
         <v>18</v>
       </c>
-      <c r="E259" t="s">
+      <c r="G259" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>26</v>
       </c>
@@ -4912,11 +4972,11 @@
       <c r="D260" t="s">
         <v>21</v>
       </c>
-      <c r="E260" t="s">
+      <c r="G260" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>26</v>
       </c>
@@ -4929,11 +4989,11 @@
       <c r="D261" t="s">
         <v>22</v>
       </c>
-      <c r="E261" t="s">
+      <c r="G261" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>27</v>
       </c>
@@ -4946,11 +5006,11 @@
       <c r="D262" t="s">
         <v>6</v>
       </c>
-      <c r="E262" t="s">
+      <c r="G262" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>27</v>
       </c>
@@ -4963,11 +5023,11 @@
       <c r="D263" t="s">
         <v>10</v>
       </c>
-      <c r="E263" t="s">
+      <c r="G263" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>27</v>
       </c>
@@ -4980,11 +5040,11 @@
       <c r="D264" t="s">
         <v>11</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>27</v>
       </c>
@@ -4997,11 +5057,11 @@
       <c r="D265" t="s">
         <v>12</v>
       </c>
-      <c r="E265" t="s">
+      <c r="G265" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>27</v>
       </c>
@@ -5014,11 +5074,11 @@
       <c r="D266" t="s">
         <v>13</v>
       </c>
-      <c r="E266" t="s">
+      <c r="G266" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>27</v>
       </c>
@@ -5031,11 +5091,11 @@
       <c r="D267" t="s">
         <v>14</v>
       </c>
-      <c r="E267" t="s">
+      <c r="G267" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>27</v>
       </c>
@@ -5048,11 +5108,11 @@
       <c r="D268" t="s">
         <v>15</v>
       </c>
-      <c r="E268" t="s">
+      <c r="G268" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>27</v>
       </c>
@@ -5065,11 +5125,11 @@
       <c r="D269" t="s">
         <v>19</v>
       </c>
-      <c r="E269" t="s">
+      <c r="G269" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>27</v>
       </c>
@@ -5082,11 +5142,11 @@
       <c r="D270" t="s">
         <v>20</v>
       </c>
-      <c r="E270" t="s">
+      <c r="G270" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>27</v>
       </c>
@@ -5099,11 +5159,11 @@
       <c r="D271" t="s">
         <v>23</v>
       </c>
-      <c r="E271" t="s">
+      <c r="G271" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>28</v>
       </c>
@@ -5116,11 +5176,11 @@
       <c r="D272" t="s">
         <v>5</v>
       </c>
-      <c r="E272" t="s">
+      <c r="G272" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>28</v>
       </c>
@@ -5133,11 +5193,11 @@
       <c r="D273" t="s">
         <v>7</v>
       </c>
-      <c r="E273" t="s">
+      <c r="G273" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>28</v>
       </c>
@@ -5150,11 +5210,11 @@
       <c r="D274" t="s">
         <v>24</v>
       </c>
-      <c r="E274" t="s">
+      <c r="G274" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>28</v>
       </c>
@@ -5167,11 +5227,11 @@
       <c r="D275" t="s">
         <v>8</v>
       </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>28</v>
       </c>
@@ -5184,11 +5244,11 @@
       <c r="D276" t="s">
         <v>9</v>
       </c>
-      <c r="E276" t="s">
+      <c r="G276" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>28</v>
       </c>
@@ -5201,11 +5261,11 @@
       <c r="D277" t="s">
         <v>16</v>
       </c>
-      <c r="E277" t="s">
+      <c r="G277" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>28</v>
       </c>
@@ -5218,11 +5278,11 @@
       <c r="D278" t="s">
         <v>17</v>
       </c>
-      <c r="E278" t="s">
+      <c r="G278" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>28</v>
       </c>
@@ -5235,11 +5295,11 @@
       <c r="D279" t="s">
         <v>18</v>
       </c>
-      <c r="E279" t="s">
+      <c r="G279" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>28</v>
       </c>
@@ -5252,11 +5312,11 @@
       <c r="D280" t="s">
         <v>21</v>
       </c>
-      <c r="E280" t="s">
+      <c r="G280" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>28</v>
       </c>
@@ -5269,11 +5329,11 @@
       <c r="D281" t="s">
         <v>22</v>
       </c>
-      <c r="E281" t="s">
+      <c r="G281" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>29</v>
       </c>
@@ -5286,11 +5346,11 @@
       <c r="D282" t="s">
         <v>6</v>
       </c>
-      <c r="E282" t="s">
+      <c r="G282" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>29</v>
       </c>
@@ -5303,11 +5363,11 @@
       <c r="D283" t="s">
         <v>7</v>
       </c>
-      <c r="E283" t="s">
+      <c r="G283" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>29</v>
       </c>
@@ -5320,11 +5380,11 @@
       <c r="D284" t="s">
         <v>9</v>
       </c>
-      <c r="E284" t="s">
+      <c r="G284" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>29</v>
       </c>
@@ -5337,11 +5397,11 @@
       <c r="D285" t="s">
         <v>10</v>
       </c>
-      <c r="E285" t="s">
+      <c r="G285" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>29</v>
       </c>
@@ -5354,11 +5414,11 @@
       <c r="D286" t="s">
         <v>11</v>
       </c>
-      <c r="E286" t="s">
+      <c r="G286" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>29</v>
       </c>
@@ -5371,11 +5431,11 @@
       <c r="D287" t="s">
         <v>16</v>
       </c>
-      <c r="E287" t="s">
+      <c r="G287" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>29</v>
       </c>
@@ -5388,11 +5448,11 @@
       <c r="D288" t="s">
         <v>17</v>
       </c>
-      <c r="E288" t="s">
+      <c r="G288" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>29</v>
       </c>
@@ -5405,11 +5465,11 @@
       <c r="D289" t="s">
         <v>19</v>
       </c>
-      <c r="E289" t="s">
+      <c r="G289" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>29</v>
       </c>
@@ -5422,11 +5482,11 @@
       <c r="D290" t="s">
         <v>22</v>
       </c>
-      <c r="E290" t="s">
+      <c r="G290" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>29</v>
       </c>
@@ -5439,11 +5499,11 @@
       <c r="D291" t="s">
         <v>23</v>
       </c>
-      <c r="E291" t="s">
+      <c r="G291" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>30</v>
       </c>
@@ -5456,11 +5516,11 @@
       <c r="D292" t="s">
         <v>5</v>
       </c>
-      <c r="E292" t="s">
+      <c r="G292" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>30</v>
       </c>
@@ -5473,11 +5533,11 @@
       <c r="D293" t="s">
         <v>24</v>
       </c>
-      <c r="E293" t="s">
+      <c r="G293" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>30</v>
       </c>
@@ -5490,11 +5550,11 @@
       <c r="D294" t="s">
         <v>8</v>
       </c>
-      <c r="E294" t="s">
+      <c r="G294" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>30</v>
       </c>
@@ -5507,11 +5567,11 @@
       <c r="D295" t="s">
         <v>12</v>
       </c>
-      <c r="E295" t="s">
+      <c r="G295" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>30</v>
       </c>
@@ -5524,11 +5584,11 @@
       <c r="D296" t="s">
         <v>13</v>
       </c>
-      <c r="E296" t="s">
+      <c r="G296" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>30</v>
       </c>
@@ -5541,11 +5601,11 @@
       <c r="D297" t="s">
         <v>14</v>
       </c>
-      <c r="E297" t="s">
+      <c r="G297" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>30</v>
       </c>
@@ -5558,11 +5618,11 @@
       <c r="D298" t="s">
         <v>15</v>
       </c>
-      <c r="E298" t="s">
+      <c r="G298" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>30</v>
       </c>
@@ -5575,11 +5635,11 @@
       <c r="D299" t="s">
         <v>18</v>
       </c>
-      <c r="E299" t="s">
+      <c r="G299" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>30</v>
       </c>
@@ -5592,11 +5652,11 @@
       <c r="D300" t="s">
         <v>20</v>
       </c>
-      <c r="E300" t="s">
+      <c r="G300" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>30</v>
       </c>
@@ -5609,11 +5669,11 @@
       <c r="D301" t="s">
         <v>21</v>
       </c>
-      <c r="E301" t="s">
+      <c r="G301" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>31</v>
       </c>
@@ -5626,11 +5686,11 @@
       <c r="D302" t="s">
         <v>23</v>
       </c>
-      <c r="E302" t="s">
+      <c r="G302" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>31</v>
       </c>
@@ -5643,11 +5703,11 @@
       <c r="D303" t="s">
         <v>6</v>
       </c>
-      <c r="E303" t="s">
+      <c r="G303" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>31</v>
       </c>
@@ -5660,11 +5720,11 @@
       <c r="D304" t="s">
         <v>7</v>
       </c>
-      <c r="E304" t="s">
+      <c r="G304" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>31</v>
       </c>
@@ -5677,11 +5737,11 @@
       <c r="D305" t="s">
         <v>9</v>
       </c>
-      <c r="E305" t="s">
+      <c r="G305" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>31</v>
       </c>
@@ -5694,11 +5754,11 @@
       <c r="D306" t="s">
         <v>10</v>
       </c>
-      <c r="E306" t="s">
+      <c r="G306" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>31</v>
       </c>
@@ -5711,11 +5771,11 @@
       <c r="D307" t="s">
         <v>11</v>
       </c>
-      <c r="E307" t="s">
+      <c r="G307" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>31</v>
       </c>
@@ -5728,11 +5788,11 @@
       <c r="D308" t="s">
         <v>16</v>
       </c>
-      <c r="E308" t="s">
+      <c r="G308" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>31</v>
       </c>
@@ -5745,11 +5805,11 @@
       <c r="D309" t="s">
         <v>17</v>
       </c>
-      <c r="E309" t="s">
+      <c r="G309" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>31</v>
       </c>
@@ -5762,11 +5822,11 @@
       <c r="D310" t="s">
         <v>19</v>
       </c>
-      <c r="E310" t="s">
+      <c r="G310" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>31</v>
       </c>
@@ -5779,11 +5839,11 @@
       <c r="D311" t="s">
         <v>22</v>
       </c>
-      <c r="E311" t="s">
+      <c r="G311" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>32</v>
       </c>
@@ -5796,11 +5856,11 @@
       <c r="D312" t="s">
         <v>5</v>
       </c>
-      <c r="E312" t="s">
+      <c r="G312" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>32</v>
       </c>
@@ -5813,11 +5873,11 @@
       <c r="D313" t="s">
         <v>24</v>
       </c>
-      <c r="E313" t="s">
+      <c r="G313" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>32</v>
       </c>
@@ -5830,11 +5890,11 @@
       <c r="D314" t="s">
         <v>8</v>
       </c>
-      <c r="E314" t="s">
+      <c r="G314" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>32</v>
       </c>
@@ -5847,11 +5907,11 @@
       <c r="D315" t="s">
         <v>12</v>
       </c>
-      <c r="E315" t="s">
+      <c r="G315" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>32</v>
       </c>
@@ -5864,11 +5924,11 @@
       <c r="D316" t="s">
         <v>13</v>
       </c>
-      <c r="E316" t="s">
+      <c r="G316" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>32</v>
       </c>
@@ -5881,11 +5941,11 @@
       <c r="D317" t="s">
         <v>14</v>
       </c>
-      <c r="E317" t="s">
+      <c r="G317" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>32</v>
       </c>
@@ -5898,11 +5958,11 @@
       <c r="D318" t="s">
         <v>15</v>
       </c>
-      <c r="E318" t="s">
+      <c r="G318" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>32</v>
       </c>
@@ -5915,11 +5975,11 @@
       <c r="D319" t="s">
         <v>18</v>
       </c>
-      <c r="E319" t="s">
+      <c r="G319" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>32</v>
       </c>
@@ -5932,11 +5992,11 @@
       <c r="D320" t="s">
         <v>20</v>
       </c>
-      <c r="E320" t="s">
+      <c r="G320" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>32</v>
       </c>
@@ -5949,11 +6009,11 @@
       <c r="D321" t="s">
         <v>21</v>
       </c>
-      <c r="E321" t="s">
+      <c r="G321" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>33</v>
       </c>
@@ -5966,11 +6026,11 @@
       <c r="D322" t="s">
         <v>6</v>
       </c>
-      <c r="E322" t="s">
+      <c r="G322" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>33</v>
       </c>
@@ -5983,11 +6043,11 @@
       <c r="D323" t="s">
         <v>7</v>
       </c>
-      <c r="E323" t="s">
+      <c r="G323" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>33</v>
       </c>
@@ -6000,11 +6060,11 @@
       <c r="D324" t="s">
         <v>24</v>
       </c>
-      <c r="E324" t="s">
+      <c r="G324" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>33</v>
       </c>
@@ -6017,11 +6077,11 @@
       <c r="D325" t="s">
         <v>9</v>
       </c>
-      <c r="E325" t="s">
+      <c r="G325" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>33</v>
       </c>
@@ -6034,11 +6094,11 @@
       <c r="D326" t="s">
         <v>12</v>
       </c>
-      <c r="E326" t="s">
+      <c r="G326" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>33</v>
       </c>
@@ -6051,11 +6111,11 @@
       <c r="D327" t="s">
         <v>16</v>
       </c>
-      <c r="E327" t="s">
+      <c r="G327" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>33</v>
       </c>
@@ -6068,11 +6128,11 @@
       <c r="D328" t="s">
         <v>19</v>
       </c>
-      <c r="E328" t="s">
+      <c r="G328" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>33</v>
       </c>
@@ -6085,11 +6145,11 @@
       <c r="D329" t="s">
         <v>20</v>
       </c>
-      <c r="E329" t="s">
+      <c r="G329" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>33</v>
       </c>
@@ -6102,11 +6162,11 @@
       <c r="D330" t="s">
         <v>21</v>
       </c>
-      <c r="E330" t="s">
+      <c r="G330" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>33</v>
       </c>
@@ -6119,11 +6179,11 @@
       <c r="D331" t="s">
         <v>23</v>
       </c>
-      <c r="E331" t="s">
+      <c r="G331" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>34</v>
       </c>
@@ -6136,11 +6196,11 @@
       <c r="D332" t="s">
         <v>22</v>
       </c>
-      <c r="E332" t="s">
+      <c r="G332" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>34</v>
       </c>
@@ -6153,11 +6213,11 @@
       <c r="D333" t="s">
         <v>5</v>
       </c>
-      <c r="E333" t="s">
+      <c r="G333" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>34</v>
       </c>
@@ -6170,11 +6230,11 @@
       <c r="D334" t="s">
         <v>8</v>
       </c>
-      <c r="E334" t="s">
+      <c r="G334" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>34</v>
       </c>
@@ -6187,11 +6247,11 @@
       <c r="D335" t="s">
         <v>10</v>
       </c>
-      <c r="E335" t="s">
+      <c r="G335" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>34</v>
       </c>
@@ -6204,11 +6264,11 @@
       <c r="D336" t="s">
         <v>11</v>
       </c>
-      <c r="E336" t="s">
+      <c r="G336" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>34</v>
       </c>
@@ -6221,11 +6281,11 @@
       <c r="D337" t="s">
         <v>13</v>
       </c>
-      <c r="E337" t="s">
+      <c r="G337" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>34</v>
       </c>
@@ -6238,11 +6298,11 @@
       <c r="D338" t="s">
         <v>14</v>
       </c>
-      <c r="E338" t="s">
+      <c r="G338" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>34</v>
       </c>
@@ -6255,11 +6315,11 @@
       <c r="D339" t="s">
         <v>15</v>
       </c>
-      <c r="E339" t="s">
+      <c r="G339" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>34</v>
       </c>
@@ -6272,11 +6332,11 @@
       <c r="D340" t="s">
         <v>17</v>
       </c>
-      <c r="E340" t="s">
+      <c r="G340" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>34</v>
       </c>
@@ -6289,11 +6349,11 @@
       <c r="D341" t="s">
         <v>18</v>
       </c>
-      <c r="E341" t="s">
+      <c r="G341" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>35</v>
       </c>
@@ -6306,11 +6366,11 @@
       <c r="D342" t="s">
         <v>7</v>
       </c>
-      <c r="E342" t="s">
+      <c r="G342" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>35</v>
       </c>
@@ -6323,11 +6383,11 @@
       <c r="D343" t="s">
         <v>24</v>
       </c>
-      <c r="E343" t="s">
+      <c r="G343" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>35</v>
       </c>
@@ -6340,11 +6400,11 @@
       <c r="D344" t="s">
         <v>8</v>
       </c>
-      <c r="E344" t="s">
+      <c r="G344" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>35</v>
       </c>
@@ -6357,11 +6417,11 @@
       <c r="D345" t="s">
         <v>12</v>
       </c>
-      <c r="E345" t="s">
+      <c r="G345" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>35</v>
       </c>
@@ -6374,11 +6434,11 @@
       <c r="D346" t="s">
         <v>13</v>
       </c>
-      <c r="E346" t="s">
+      <c r="G346" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>35</v>
       </c>
@@ -6391,11 +6451,11 @@
       <c r="D347" t="s">
         <v>16</v>
       </c>
-      <c r="E347" t="s">
+      <c r="G347" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>35</v>
       </c>
@@ -6408,11 +6468,11 @@
       <c r="D348" t="s">
         <v>18</v>
       </c>
-      <c r="E348" t="s">
+      <c r="G348" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>35</v>
       </c>
@@ -6425,11 +6485,11 @@
       <c r="D349" t="s">
         <v>20</v>
       </c>
-      <c r="E349" t="s">
+      <c r="G349" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>35</v>
       </c>
@@ -6442,11 +6502,11 @@
       <c r="D350" t="s">
         <v>21</v>
       </c>
-      <c r="E350" t="s">
+      <c r="G350" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>35</v>
       </c>
@@ -6459,11 +6519,11 @@
       <c r="D351" t="s">
         <v>23</v>
       </c>
-      <c r="E351" t="s">
+      <c r="G351" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>36</v>
       </c>
@@ -6476,11 +6536,11 @@
       <c r="D352" t="s">
         <v>5</v>
       </c>
-      <c r="E352" t="s">
+      <c r="G352" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>36</v>
       </c>
@@ -6493,11 +6553,11 @@
       <c r="D353" t="s">
         <v>6</v>
       </c>
-      <c r="E353" t="s">
+      <c r="G353" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>36</v>
       </c>
@@ -6510,11 +6570,11 @@
       <c r="D354" t="s">
         <v>9</v>
       </c>
-      <c r="E354" t="s">
+      <c r="G354" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>36</v>
       </c>
@@ -6527,11 +6587,11 @@
       <c r="D355" t="s">
         <v>10</v>
       </c>
-      <c r="E355" t="s">
+      <c r="G355" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>36</v>
       </c>
@@ -6544,11 +6604,11 @@
       <c r="D356" t="s">
         <v>11</v>
       </c>
-      <c r="E356" t="s">
+      <c r="G356" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>36</v>
       </c>
@@ -6561,11 +6621,11 @@
       <c r="D357" t="s">
         <v>14</v>
       </c>
-      <c r="E357" t="s">
+      <c r="G357" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>36</v>
       </c>
@@ -6578,11 +6638,11 @@
       <c r="D358" t="s">
         <v>15</v>
       </c>
-      <c r="E358" t="s">
+      <c r="G358" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>36</v>
       </c>
@@ -6595,11 +6655,11 @@
       <c r="D359" t="s">
         <v>17</v>
       </c>
-      <c r="E359" t="s">
+      <c r="G359" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>36</v>
       </c>
@@ -6612,11 +6672,11 @@
       <c r="D360" t="s">
         <v>19</v>
       </c>
-      <c r="E360" t="s">
+      <c r="G360" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>36</v>
       </c>
@@ -6629,11 +6689,11 @@
       <c r="D361" t="s">
         <v>22</v>
       </c>
-      <c r="E361" t="s">
+      <c r="G361" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>37</v>
       </c>
@@ -6646,11 +6706,11 @@
       <c r="D362" t="s">
         <v>7</v>
       </c>
-      <c r="E362" t="s">
+      <c r="G362" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>37</v>
       </c>
@@ -6663,11 +6723,11 @@
       <c r="D363" t="s">
         <v>24</v>
       </c>
-      <c r="E363" t="s">
+      <c r="G363" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>37</v>
       </c>
@@ -6680,11 +6740,11 @@
       <c r="D364" t="s">
         <v>8</v>
       </c>
-      <c r="E364" t="s">
+      <c r="G364" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>37</v>
       </c>
@@ -6697,11 +6757,11 @@
       <c r="D365" t="s">
         <v>12</v>
       </c>
-      <c r="E365" t="s">
+      <c r="G365" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>37</v>
       </c>
@@ -6714,11 +6774,11 @@
       <c r="D366" t="s">
         <v>13</v>
       </c>
-      <c r="E366" t="s">
+      <c r="G366" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>37</v>
       </c>
@@ -6731,11 +6791,11 @@
       <c r="D367" t="s">
         <v>16</v>
       </c>
-      <c r="E367" t="s">
+      <c r="G367" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>37</v>
       </c>
@@ -6748,11 +6808,11 @@
       <c r="D368" t="s">
         <v>18</v>
       </c>
-      <c r="E368" t="s">
+      <c r="G368" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>37</v>
       </c>
@@ -6765,11 +6825,11 @@
       <c r="D369" t="s">
         <v>20</v>
       </c>
-      <c r="E369" t="s">
+      <c r="G369" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>37</v>
       </c>
@@ -6782,11 +6842,11 @@
       <c r="D370" t="s">
         <v>21</v>
       </c>
-      <c r="E370" t="s">
+      <c r="G370" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>37</v>
       </c>
@@ -6799,11 +6859,11 @@
       <c r="D371" t="s">
         <v>23</v>
       </c>
-      <c r="E371" t="s">
+      <c r="G371" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>38</v>
       </c>
@@ -6816,11 +6876,11 @@
       <c r="D372" t="s">
         <v>22</v>
       </c>
-      <c r="E372" t="s">
+      <c r="G372" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>38</v>
       </c>
@@ -6833,11 +6893,11 @@
       <c r="D373" t="s">
         <v>5</v>
       </c>
-      <c r="E373" t="s">
+      <c r="G373" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>38</v>
       </c>
@@ -6850,11 +6910,11 @@
       <c r="D374" t="s">
         <v>6</v>
       </c>
-      <c r="E374" t="s">
+      <c r="G374" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>38</v>
       </c>
@@ -6867,11 +6927,11 @@
       <c r="D375" t="s">
         <v>9</v>
       </c>
-      <c r="E375" t="s">
+      <c r="G375" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>38</v>
       </c>
@@ -6884,11 +6944,11 @@
       <c r="D376" t="s">
         <v>10</v>
       </c>
-      <c r="E376" t="s">
+      <c r="G376" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>38</v>
       </c>
@@ -6901,11 +6961,11 @@
       <c r="D377" t="s">
         <v>11</v>
       </c>
-      <c r="E377" t="s">
+      <c r="G377" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>38</v>
       </c>
@@ -6918,11 +6978,11 @@
       <c r="D378" t="s">
         <v>14</v>
       </c>
-      <c r="E378" t="s">
+      <c r="G378" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>38</v>
       </c>
@@ -6935,11 +6995,11 @@
       <c r="D379" t="s">
         <v>15</v>
       </c>
-      <c r="E379" t="s">
+      <c r="G379" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>38</v>
       </c>
@@ -6952,11 +7012,11 @@
       <c r="D380" t="s">
         <v>17</v>
       </c>
-      <c r="E380" t="s">
+      <c r="G380" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>38</v>
       </c>
@@ -6969,13 +7029,13 @@
       <c r="D381" t="s">
         <v>19</v>
       </c>
-      <c r="E381" t="s">
+      <c r="G381" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E381" xr:uid="{8F4EEE65-7860-43B6-A275-4EB8A0B58B8B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E381">
+  <autoFilter ref="A1:G381" xr:uid="{8F4EEE65-7860-43B6-A275-4EB8A0B58B8B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G381">
       <sortCondition ref="B1:B381"/>
     </sortState>
   </autoFilter>

--- a/PL2627.xlsx
+++ b/PL2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf7844e8cf3277c/Documents/LMS_2627_1_repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{68010DEC-8158-4E01-AB72-369A3BA3C3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE2538F-6084-4796-B45D-94F5BB874201}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{68010DEC-8158-4E01-AB72-369A3BA3C3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A53DADC6-1A34-431C-850A-F2C60C76A663}"/>
   <bookViews>
     <workbookView xWindow="1335" yWindow="-16860" windowWidth="21600" windowHeight="12525" xr2:uid="{36BCC181-D9F5-4121-8B79-8FE9A95C768C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="27">
   <si>
     <t>GW</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Brentford</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>AS</t>
   </si>
 </sst>
 </file>
@@ -509,6 +515,12 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
       <c r="G1" t="s">
         <v>4</v>
       </c>
